--- a/artfynd/A 50278-2025 artfynd.xlsx
+++ b/artfynd/A 50278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134037142</v>
       </c>
       <c r="B2" t="n">
-        <v>91931</v>
+        <v>91947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134037144</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>134037145</v>
       </c>
       <c r="B4" t="n">
-        <v>91927</v>
+        <v>91943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>134037143</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50278-2025 artfynd.xlsx
+++ b/artfynd/A 50278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134037142</v>
       </c>
       <c r="B2" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134037144</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>134037145</v>
       </c>
       <c r="B4" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>134037143</v>
       </c>
       <c r="B5" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
